--- a/runway-app/Round trip - SF-424A.xlsx
+++ b/runway-app/Round trip - SF-424A.xlsx
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -764,10 +764,10 @@
         <v>BP2</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -775,10 +775,10 @@
         <v>BP3</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C10">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
